--- a/Configs/GameConfig/Datas/expedition_environment.xlsx
+++ b/Configs/GameConfig/Datas/expedition_environment.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -49,12 +49,18 @@
     <t>*lst_battlefield</t>
   </si>
   <si>
+    <t>*lst_enemy_candidate</t>
+  </si>
+  <si>
     <t>battlefield_config_id</t>
   </si>
   <si>
     <t>weight</t>
   </si>
   <si>
+    <t>marble_spawn_config</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -68,6 +74,24 @@
   </si>
   <si>
     <t>普通森林_1</t>
+  </si>
+  <si>
+    <t>lancer,0,hollow</t>
+  </si>
+  <si>
+    <t>soldier,0,hollow</t>
+  </si>
+  <si>
+    <t>archer,0,hollow</t>
+  </si>
+  <si>
+    <t>lancer,1,hollow</t>
+  </si>
+  <si>
+    <t>soldier,1,hollow</t>
+  </si>
+  <si>
+    <t>archer,1,hollow</t>
   </si>
 </sst>
 </file>
@@ -750,7 +774,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -782,6 +806,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1125,8 +1152,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="5" customWidth="1"/>
     <col min="2" max="2" width="33.6363636363636" style="5" customWidth="1"/>
@@ -1135,9 +1162,11 @@
     <col min="5" max="5" width="39.8181818181818" style="5" customWidth="1"/>
     <col min="6" max="6" width="26.2727272727273" style="6" customWidth="1"/>
     <col min="7" max="7" width="8.09090909090909" style="6" customWidth="1"/>
+    <col min="8" max="8" width="23.8181818181818" style="6" customWidth="1"/>
+    <col min="9" max="9" width="8.09090909090909" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:9">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1157,8 +1186,12 @@
         <v>5</v>
       </c>
       <c r="G1" s="10"/>
+      <c r="H1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="11"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
+    <row r="2" s="1" customFormat="1" spans="1:9">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1166,14 +1199,20 @@
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
-      <c r="F2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>7</v>
       </c>
+      <c r="G2" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:7">
+    <row r="3" s="1" customFormat="1" spans="1:9">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
@@ -1181,82 +1220,139 @@
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:7">
-      <c r="A4" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
+    <row r="4" s="2" customFormat="1" spans="1:9">
+      <c r="A4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="14"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
     </row>
-    <row r="5" s="3" customFormat="1" spans="1:7">
-      <c r="A5" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
+    <row r="5" s="3" customFormat="1" spans="1:9">
+      <c r="A5" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:7">
-      <c r="A6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+    <row r="6" s="3" customFormat="1" spans="1:9">
+      <c r="A6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
     </row>
-    <row r="7" s="4" customFormat="1" ht="57" customHeight="1" spans="1:7">
-      <c r="A7" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
+    <row r="7" s="4" customFormat="1" ht="57" customHeight="1" spans="1:9">
+      <c r="A7" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9">
       <c r="B8" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G8" s="6">
         <v>10</v>
       </c>
+      <c r="H8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="H9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="H10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="H11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="H12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="H13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="6">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
